--- a/research/traditional_assets/database/data/italy/italy_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.016265</v>
+        <v>-0.014</v>
       </c>
       <c r="E2">
-        <v>0.266</v>
+        <v>0.277</v>
       </c>
       <c r="F2">
-        <v>0.0825</v>
+        <v>0.0515</v>
       </c>
       <c r="G2">
-        <v>0.08079631516010453</v>
+        <v>0.1040066512294057</v>
       </c>
       <c r="H2">
-        <v>0.08079631516010453</v>
+        <v>0.1040066512294057</v>
       </c>
       <c r="I2">
-        <v>0.0703839851189158</v>
+        <v>0.08588789690594421</v>
       </c>
       <c r="J2">
-        <v>0.04395048275109872</v>
+        <v>0.06143158940948207</v>
       </c>
       <c r="K2">
-        <v>1844.5</v>
+        <v>1792.5</v>
       </c>
       <c r="L2">
-        <v>0.0408454758846716</v>
+        <v>0.05821449565299289</v>
       </c>
       <c r="M2">
-        <v>732.5</v>
+        <v>797.2</v>
       </c>
       <c r="N2">
-        <v>0.04000436907785151</v>
+        <v>0.06294413037299056</v>
       </c>
       <c r="O2">
-        <v>0.3971265925725129</v>
+        <v>0.4447419804741981</v>
       </c>
       <c r="P2">
-        <v>732.5</v>
+        <v>752.1</v>
       </c>
       <c r="Q2">
-        <v>0.04000436907785151</v>
+        <v>0.05938319173799071</v>
       </c>
       <c r="R2">
-        <v>0.3971265925725129</v>
+        <v>0.419581589958159</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>45.10000000000002</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.05657300551931764</v>
       </c>
       <c r="U2">
-        <v>8219.700000000001</v>
+        <v>5509.9</v>
       </c>
       <c r="V2">
-        <v>0.448906365200295</v>
+        <v>0.4350424786027856</v>
       </c>
       <c r="W2">
-        <v>0.09797920590869676</v>
+        <v>0.1217383626954266</v>
       </c>
       <c r="X2">
-        <v>0.253248527575029</v>
+        <v>0.5825835945564195</v>
       </c>
       <c r="Y2">
-        <v>-0.1552693216663322</v>
+        <v>-0.4608452318609929</v>
       </c>
       <c r="Z2">
-        <v>0.3827971026163764</v>
+        <v>0.2538917010850341</v>
       </c>
       <c r="AA2">
-        <v>0.06162040860057991</v>
+        <v>0.01559697073553076</v>
       </c>
       <c r="AB2">
-        <v>0.0806057286824583</v>
+        <v>0.1234795054755359</v>
       </c>
       <c r="AC2">
-        <v>-0.01898532008187839</v>
+        <v>-0.1078825347400051</v>
       </c>
       <c r="AD2">
-        <v>115811.3</v>
+        <v>99645</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>115811.3</v>
+        <v>99645</v>
       </c>
       <c r="AG2">
-        <v>107591.6</v>
+        <v>94135.10000000001</v>
       </c>
       <c r="AH2">
-        <v>0.8634785694793837</v>
+        <v>0.8872301892437197</v>
       </c>
       <c r="AI2">
-        <v>0.8665507387784025</v>
+        <v>0.9141516678027242</v>
       </c>
       <c r="AJ2">
-        <v>0.8545655711858658</v>
+        <v>0.8814123181301925</v>
       </c>
       <c r="AK2">
-        <v>0.857805282133136</v>
+        <v>0.9095811496065427</v>
       </c>
       <c r="AL2">
-        <v>195.8</v>
+        <v>84.3</v>
       </c>
       <c r="AM2">
-        <v>38.20000000000002</v>
+        <v>-76.50000000000001</v>
       </c>
       <c r="AN2">
-        <v>30.39267812623016</v>
+        <v>30.98125174890402</v>
       </c>
       <c r="AO2">
-        <v>16.23289070480081</v>
+        <v>31.37129300118624</v>
       </c>
       <c r="AP2">
-        <v>28.2355596378428</v>
+        <v>29.26813419146224</v>
       </c>
       <c r="AQ2">
-        <v>83.20418848167535</v>
+        <v>-34.56993464052287</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Società Cattolica di Assicurazione - Società Cooperativa (BIT:CASS)</t>
+          <t>Poste Italiane S.p.A. (BIT:PST)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,255 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0282</v>
+        <v>-0.014</v>
       </c>
       <c r="E3">
-        <v>0.382</v>
+        <v>0.277</v>
+      </c>
+      <c r="F3">
+        <v>0.0515</v>
       </c>
       <c r="G3">
-        <v>0.07672996365653234</v>
+        <v>0.1040066512294057</v>
       </c>
       <c r="H3">
-        <v>0.07672996365653234</v>
+        <v>0.1040066512294057</v>
       </c>
       <c r="I3">
-        <v>0.0584122721235386</v>
+        <v>0.08588789690594421</v>
       </c>
       <c r="J3">
-        <v>0.0292061360617693</v>
+        <v>0.06143158940948207</v>
       </c>
       <c r="K3">
-        <v>128</v>
+        <v>1792.5</v>
       </c>
       <c r="L3">
-        <v>0.01868258578663903</v>
+        <v>0.05821449565299289</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>797.2</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.06294413037299056</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.4447419804741981</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>752.1</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.05938319173799071</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.419581589958159</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>45.10000000000002</v>
+      </c>
+      <c r="T3">
+        <v>0.05657300551931764</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>5509.9</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.4350424786027856</v>
       </c>
       <c r="W3">
-        <v>0.05627610463838206</v>
+        <v>0.1217383626954266</v>
       </c>
       <c r="X3">
-        <v>0.1137157885751033</v>
+        <v>0.5825835945564195</v>
       </c>
       <c r="Y3">
-        <v>-0.05743968393672128</v>
+        <v>-0.4608452318609929</v>
       </c>
       <c r="Z3">
-        <v>3.605947368421053</v>
+        <v>0.2538917010850341</v>
       </c>
       <c r="AA3">
-        <v>0.1053157894736842</v>
+        <v>0.01559697073553076</v>
       </c>
       <c r="AB3">
-        <v>0.07761907400650385</v>
+        <v>0.1234795054755359</v>
       </c>
       <c r="AC3">
-        <v>0.02769671546718036</v>
+        <v>-0.1078825347400051</v>
       </c>
       <c r="AD3">
-        <v>1038.5</v>
+        <v>99645</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1038.5</v>
+        <v>99645</v>
       </c>
       <c r="AG3">
-        <v>1038.5</v>
+        <v>94135.10000000001</v>
       </c>
       <c r="AH3">
-        <v>0.4416142201054601</v>
+        <v>0.8872301892437197</v>
       </c>
       <c r="AI3">
-        <v>0.2507727228822564</v>
+        <v>0.9141516678027242</v>
       </c>
       <c r="AJ3">
-        <v>0.4416142201054601</v>
+        <v>0.8814123181301925</v>
       </c>
       <c r="AK3">
-        <v>0.2507727228822564</v>
+        <v>0.9095811496065427</v>
       </c>
       <c r="AL3">
-        <v>151.8</v>
+        <v>84.3</v>
       </c>
       <c r="AM3">
-        <v>151.8</v>
+        <v>-76.50000000000001</v>
       </c>
       <c r="AN3">
-        <v>2.767857142857143</v>
+        <v>30.98125174890402</v>
       </c>
       <c r="AO3">
-        <v>2.636363636363636</v>
+        <v>31.37129300118624</v>
       </c>
       <c r="AP3">
-        <v>2.767857142857143</v>
+        <v>29.26813419146224</v>
       </c>
       <c r="AQ3">
-        <v>2.636363636363636</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Poste Italiane SpA (BIT:PST)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.00433</v>
-      </c>
-      <c r="E4">
-        <v>0.15</v>
-      </c>
-      <c r="F4">
-        <v>0.0825</v>
-      </c>
-      <c r="G4">
-        <v>0.08152359769961913</v>
-      </c>
-      <c r="H4">
-        <v>0.08152359769961913</v>
-      </c>
-      <c r="I4">
-        <v>0.07252517183678051</v>
-      </c>
-      <c r="J4">
-        <v>0.05431245919869115</v>
-      </c>
-      <c r="K4">
-        <v>1716.5</v>
-      </c>
-      <c r="L4">
-        <v>0.04480939365698429</v>
-      </c>
-      <c r="M4">
-        <v>732.5</v>
-      </c>
-      <c r="N4">
-        <v>0.0430948262675468</v>
-      </c>
-      <c r="O4">
-        <v>0.4267404602388581</v>
-      </c>
-      <c r="P4">
-        <v>732.5</v>
-      </c>
-      <c r="Q4">
-        <v>0.0430948262675468</v>
-      </c>
-      <c r="R4">
-        <v>0.4267404602388581</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>8219.700000000001</v>
-      </c>
-      <c r="V4">
-        <v>0.4835857248755692</v>
-      </c>
-      <c r="W4">
-        <v>0.1396823071790115</v>
-      </c>
-      <c r="X4">
-        <v>0.3927812665749546</v>
-      </c>
-      <c r="Y4">
-        <v>-0.2530989593959432</v>
-      </c>
-      <c r="Z4">
-        <v>0.330035280890164</v>
-      </c>
-      <c r="AA4">
-        <v>0.0179250277274756</v>
-      </c>
-      <c r="AB4">
-        <v>0.08359238335841274</v>
-      </c>
-      <c r="AC4">
-        <v>-0.06566735563093713</v>
-      </c>
-      <c r="AD4">
-        <v>114772.8</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>114772.8</v>
-      </c>
-      <c r="AG4">
-        <v>106553.1</v>
-      </c>
-      <c r="AH4">
-        <v>0.8710072535368391</v>
-      </c>
-      <c r="AI4">
-        <v>0.8862415456997447</v>
-      </c>
-      <c r="AJ4">
-        <v>0.8624254859349012</v>
-      </c>
-      <c r="AK4">
-        <v>0.8785319585044861</v>
-      </c>
-      <c r="AL4">
-        <v>44</v>
-      </c>
-      <c r="AM4">
-        <v>-113.6</v>
-      </c>
-      <c r="AN4">
-        <v>33.40983320234041</v>
-      </c>
-      <c r="AO4">
-        <v>63.14090909090908</v>
-      </c>
-      <c r="AP4">
-        <v>31.01711640904724</v>
-      </c>
-      <c r="AQ4">
-        <v>-24.45598591549296</v>
+        <v>-34.56993464052287</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/italy/italy_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.014</v>
+        <v>0.0209</v>
       </c>
       <c r="E2">
-        <v>0.277</v>
+        <v>0.09210000000000002</v>
       </c>
       <c r="F2">
-        <v>0.0515</v>
+        <v>0.0572</v>
       </c>
       <c r="G2">
-        <v>0.1040066512294057</v>
+        <v>0.1017025725381624</v>
       </c>
       <c r="H2">
-        <v>0.1040066512294057</v>
+        <v>0.1017025725381624</v>
       </c>
       <c r="I2">
-        <v>0.08588789690594421</v>
+        <v>0.08637681327305742</v>
       </c>
       <c r="J2">
-        <v>0.06143158940948207</v>
+        <v>0.056800094197449</v>
       </c>
       <c r="K2">
-        <v>1792.5</v>
+        <v>1678.7</v>
       </c>
       <c r="L2">
-        <v>0.05821449565299289</v>
+        <v>0.04861555570357456</v>
       </c>
       <c r="M2">
-        <v>797.2</v>
+        <v>952.6</v>
       </c>
       <c r="N2">
-        <v>0.06294413037299056</v>
+        <v>0.06474678339121982</v>
       </c>
       <c r="O2">
-        <v>0.4447419804741981</v>
+        <v>0.5674629177339608</v>
       </c>
       <c r="P2">
-        <v>752.1</v>
+        <v>894.4</v>
       </c>
       <c r="Q2">
-        <v>0.05938319173799071</v>
+        <v>0.06079101728438695</v>
       </c>
       <c r="R2">
-        <v>0.419581589958159</v>
+        <v>0.5327932328587597</v>
       </c>
       <c r="S2">
-        <v>45.10000000000002</v>
+        <v>58.20000000000005</v>
       </c>
       <c r="T2">
-        <v>0.05657300551931764</v>
+        <v>0.06109594793197569</v>
       </c>
       <c r="U2">
-        <v>5509.9</v>
+        <v>5294.2</v>
       </c>
       <c r="V2">
-        <v>0.4350424786027856</v>
+        <v>0.3598387787421751</v>
       </c>
       <c r="W2">
-        <v>0.1217383626954266</v>
+        <v>0.1801663536356319</v>
       </c>
       <c r="X2">
-        <v>0.5825835945564195</v>
+        <v>0.4192227646657722</v>
       </c>
       <c r="Y2">
-        <v>-0.4608452318609929</v>
+        <v>-0.2390564110301404</v>
       </c>
       <c r="Z2">
-        <v>0.2538917010850341</v>
+        <v>0.3337770147874485</v>
       </c>
       <c r="AA2">
-        <v>0.01559697073553076</v>
+        <v>0.0189585658808704</v>
       </c>
       <c r="AB2">
-        <v>0.1234795054755359</v>
+        <v>0.1044147657859495</v>
       </c>
       <c r="AC2">
-        <v>-0.1078825347400051</v>
+        <v>-0.08545619990507909</v>
       </c>
       <c r="AD2">
-        <v>99645</v>
+        <v>101708.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>99645</v>
+        <v>101708.3</v>
       </c>
       <c r="AG2">
-        <v>94135.10000000001</v>
+        <v>96414.10000000001</v>
       </c>
       <c r="AH2">
-        <v>0.8872301892437197</v>
+        <v>0.8736250332843731</v>
       </c>
       <c r="AI2">
-        <v>0.9141516678027242</v>
+        <v>0.9138844286621806</v>
       </c>
       <c r="AJ2">
-        <v>0.8814123181301925</v>
+        <v>0.8676043942595306</v>
       </c>
       <c r="AK2">
-        <v>0.9095811496065427</v>
+        <v>0.9095832849834101</v>
       </c>
       <c r="AL2">
-        <v>84.3</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AM2">
-        <v>-76.50000000000001</v>
+        <v>-141.83</v>
       </c>
       <c r="AN2">
-        <v>30.98125174890402</v>
+        <v>27.77245917754356</v>
       </c>
       <c r="AO2">
-        <v>31.37129300118624</v>
+        <v>352.1369539551357</v>
       </c>
       <c r="AP2">
-        <v>29.26813419146224</v>
+        <v>26.32682540549397</v>
       </c>
       <c r="AQ2">
-        <v>-34.56993464052287</v>
+        <v>-21.02940139603751</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.014</v>
+        <v>0.0209</v>
       </c>
       <c r="E3">
-        <v>0.277</v>
+        <v>0.09210000000000002</v>
       </c>
       <c r="F3">
-        <v>0.0515</v>
+        <v>0.0572</v>
       </c>
       <c r="G3">
-        <v>0.1040066512294057</v>
+        <v>0.1017025725381624</v>
       </c>
       <c r="H3">
-        <v>0.1040066512294057</v>
+        <v>0.1017025725381624</v>
       </c>
       <c r="I3">
-        <v>0.08588789690594421</v>
+        <v>0.08637681327305742</v>
       </c>
       <c r="J3">
-        <v>0.06143158940948207</v>
+        <v>0.056800094197449</v>
       </c>
       <c r="K3">
-        <v>1792.5</v>
+        <v>1678.7</v>
       </c>
       <c r="L3">
-        <v>0.05821449565299289</v>
+        <v>0.04861555570357456</v>
       </c>
       <c r="M3">
-        <v>797.2</v>
+        <v>952.6</v>
       </c>
       <c r="N3">
-        <v>0.06294413037299056</v>
+        <v>0.06474678339121982</v>
       </c>
       <c r="O3">
-        <v>0.4447419804741981</v>
+        <v>0.5674629177339608</v>
       </c>
       <c r="P3">
-        <v>752.1</v>
+        <v>894.4</v>
       </c>
       <c r="Q3">
-        <v>0.05938319173799071</v>
+        <v>0.06079101728438695</v>
       </c>
       <c r="R3">
-        <v>0.419581589958159</v>
+        <v>0.5327932328587597</v>
       </c>
       <c r="S3">
-        <v>45.10000000000002</v>
+        <v>58.20000000000005</v>
       </c>
       <c r="T3">
-        <v>0.05657300551931764</v>
+        <v>0.06109594793197569</v>
       </c>
       <c r="U3">
-        <v>5509.9</v>
+        <v>5294.2</v>
       </c>
       <c r="V3">
-        <v>0.4350424786027856</v>
+        <v>0.3598387787421751</v>
       </c>
       <c r="W3">
-        <v>0.1217383626954266</v>
+        <v>0.1801663536356319</v>
       </c>
       <c r="X3">
-        <v>0.5825835945564195</v>
+        <v>0.4192227646657722</v>
       </c>
       <c r="Y3">
-        <v>-0.4608452318609929</v>
+        <v>-0.2390564110301404</v>
       </c>
       <c r="Z3">
-        <v>0.2538917010850341</v>
+        <v>0.3337770147874485</v>
       </c>
       <c r="AA3">
-        <v>0.01559697073553076</v>
+        <v>0.0189585658808704</v>
       </c>
       <c r="AB3">
-        <v>0.1234795054755359</v>
+        <v>0.1044147657859495</v>
       </c>
       <c r="AC3">
-        <v>-0.1078825347400051</v>
+        <v>-0.08545619990507909</v>
       </c>
       <c r="AD3">
-        <v>99645</v>
+        <v>101708.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>99645</v>
+        <v>101708.3</v>
       </c>
       <c r="AG3">
-        <v>94135.10000000001</v>
+        <v>96414.10000000001</v>
       </c>
       <c r="AH3">
-        <v>0.8872301892437197</v>
+        <v>0.8736250332843731</v>
       </c>
       <c r="AI3">
-        <v>0.9141516678027242</v>
+        <v>0.9138844286621806</v>
       </c>
       <c r="AJ3">
-        <v>0.8814123181301925</v>
+        <v>0.8676043942595306</v>
       </c>
       <c r="AK3">
-        <v>0.9095811496065427</v>
+        <v>0.9095832849834101</v>
       </c>
       <c r="AL3">
-        <v>84.3</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AM3">
-        <v>-76.50000000000001</v>
+        <v>-141.83</v>
       </c>
       <c r="AN3">
-        <v>30.98125174890402</v>
+        <v>27.77245917754356</v>
       </c>
       <c r="AO3">
-        <v>31.37129300118624</v>
+        <v>352.1369539551357</v>
       </c>
       <c r="AP3">
-        <v>29.26813419146224</v>
+        <v>26.32682540549397</v>
       </c>
       <c r="AQ3">
-        <v>-34.56993464052287</v>
+        <v>-21.02940139603751</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/italy/italy_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0209</v>
+        <v>-0.165</v>
       </c>
       <c r="E2">
-        <v>0.09210000000000002</v>
+        <v>0.0687</v>
       </c>
       <c r="F2">
-        <v>0.0572</v>
+        <v>0.0341</v>
       </c>
       <c r="G2">
-        <v>0.1017025725381624</v>
+        <v>0.2533898993179604</v>
       </c>
       <c r="H2">
-        <v>0.1017025725381624</v>
+        <v>0.2533898993179604</v>
       </c>
       <c r="I2">
-        <v>0.08637681327305742</v>
+        <v>0.2181714842481325</v>
       </c>
       <c r="J2">
-        <v>0.056800094197449</v>
+        <v>0.1539649645300897</v>
       </c>
       <c r="K2">
-        <v>1678.7</v>
+        <v>2217.3</v>
       </c>
       <c r="L2">
-        <v>0.04861555570357456</v>
+        <v>0.1500284183176356</v>
       </c>
       <c r="M2">
-        <v>952.6</v>
+        <v>1204.6</v>
       </c>
       <c r="N2">
-        <v>0.06474678339121982</v>
+        <v>0.06598667776852622</v>
       </c>
       <c r="O2">
-        <v>0.5674629177339608</v>
+        <v>0.5432733504712939</v>
       </c>
       <c r="P2">
-        <v>894.4</v>
+        <v>1155.5</v>
       </c>
       <c r="Q2">
-        <v>0.06079101728438695</v>
+        <v>0.0632970331741093</v>
       </c>
       <c r="R2">
-        <v>0.5327932328587597</v>
+        <v>0.5211293014026067</v>
       </c>
       <c r="S2">
-        <v>58.20000000000005</v>
+        <v>49.09999999999991</v>
       </c>
       <c r="T2">
-        <v>0.06109594793197569</v>
+        <v>0.04076041839614802</v>
       </c>
       <c r="U2">
-        <v>5294.2</v>
+        <v>6115.3</v>
       </c>
       <c r="V2">
-        <v>0.3598387787421751</v>
+        <v>0.3349894824488365</v>
       </c>
       <c r="W2">
-        <v>0.1801663536356319</v>
+        <v>0.2343026819113638</v>
       </c>
       <c r="X2">
-        <v>0.4192227646657722</v>
+        <v>0.3027195557967973</v>
       </c>
       <c r="Y2">
-        <v>-0.2390564110301404</v>
+        <v>-0.06841687388543352</v>
       </c>
       <c r="Z2">
-        <v>0.3337770147874485</v>
+        <v>0.1395877311043423</v>
       </c>
       <c r="AA2">
-        <v>0.0189585658808704</v>
+        <v>0.02149162006831577</v>
       </c>
       <c r="AB2">
-        <v>0.1044147657859495</v>
+        <v>0.1032640455153616</v>
       </c>
       <c r="AC2">
-        <v>-0.08545619990507909</v>
+        <v>-0.08177242544704583</v>
       </c>
       <c r="AD2">
-        <v>101708.3</v>
+        <v>85087</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>101708.3</v>
+        <v>85087</v>
       </c>
       <c r="AG2">
-        <v>96414.10000000001</v>
+        <v>78971.7</v>
       </c>
       <c r="AH2">
-        <v>0.8736250332843731</v>
+        <v>0.8233519317374703</v>
       </c>
       <c r="AI2">
-        <v>0.9138844286621806</v>
+        <v>0.8636134805185315</v>
       </c>
       <c r="AJ2">
-        <v>0.8676043942595306</v>
+        <v>0.8122412624489724</v>
       </c>
       <c r="AK2">
-        <v>0.9095832849834101</v>
+        <v>0.8545879139608545</v>
       </c>
       <c r="AL2">
-        <v>8.470000000000001</v>
+        <v>53.5</v>
       </c>
       <c r="AM2">
-        <v>-141.83</v>
+        <v>-119.4</v>
       </c>
       <c r="AN2">
-        <v>27.77245917754356</v>
+        <v>21.79036058184798</v>
       </c>
       <c r="AO2">
-        <v>352.1369539551357</v>
+        <v>60.26915887850468</v>
       </c>
       <c r="AP2">
-        <v>26.32682540549397</v>
+        <v>20.22426244622003</v>
       </c>
       <c r="AQ2">
-        <v>-21.02940139603751</v>
+        <v>-27.00502512562814</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0209</v>
+        <v>-0.165</v>
       </c>
       <c r="E3">
-        <v>0.09210000000000002</v>
+        <v>0.0687</v>
       </c>
       <c r="F3">
-        <v>0.0572</v>
+        <v>0.0341</v>
       </c>
       <c r="G3">
-        <v>0.1017025725381624</v>
+        <v>0.2533898993179604</v>
       </c>
       <c r="H3">
-        <v>0.1017025725381624</v>
+        <v>0.2533898993179604</v>
       </c>
       <c r="I3">
-        <v>0.08637681327305742</v>
+        <v>0.2181714842481325</v>
       </c>
       <c r="J3">
-        <v>0.056800094197449</v>
+        <v>0.1539649645300897</v>
       </c>
       <c r="K3">
-        <v>1678.7</v>
+        <v>2217.3</v>
       </c>
       <c r="L3">
-        <v>0.04861555570357456</v>
+        <v>0.1500284183176356</v>
       </c>
       <c r="M3">
-        <v>952.6</v>
+        <v>1204.6</v>
       </c>
       <c r="N3">
-        <v>0.06474678339121982</v>
+        <v>0.06598667776852622</v>
       </c>
       <c r="O3">
-        <v>0.5674629177339608</v>
+        <v>0.5432733504712939</v>
       </c>
       <c r="P3">
-        <v>894.4</v>
+        <v>1155.5</v>
       </c>
       <c r="Q3">
-        <v>0.06079101728438695</v>
+        <v>0.0632970331741093</v>
       </c>
       <c r="R3">
-        <v>0.5327932328587597</v>
+        <v>0.5211293014026067</v>
       </c>
       <c r="S3">
-        <v>58.20000000000005</v>
+        <v>49.09999999999991</v>
       </c>
       <c r="T3">
-        <v>0.06109594793197569</v>
+        <v>0.04076041839614802</v>
       </c>
       <c r="U3">
-        <v>5294.2</v>
+        <v>6115.3</v>
       </c>
       <c r="V3">
-        <v>0.3598387787421751</v>
+        <v>0.3349894824488365</v>
       </c>
       <c r="W3">
-        <v>0.1801663536356319</v>
+        <v>0.2343026819113638</v>
       </c>
       <c r="X3">
-        <v>0.4192227646657722</v>
+        <v>0.3027195557967973</v>
       </c>
       <c r="Y3">
-        <v>-0.2390564110301404</v>
+        <v>-0.06841687388543352</v>
       </c>
       <c r="Z3">
-        <v>0.3337770147874485</v>
+        <v>0.1395877311043423</v>
       </c>
       <c r="AA3">
-        <v>0.0189585658808704</v>
+        <v>0.02149162006831577</v>
       </c>
       <c r="AB3">
-        <v>0.1044147657859495</v>
+        <v>0.1032640455153616</v>
       </c>
       <c r="AC3">
-        <v>-0.08545619990507909</v>
+        <v>-0.08177242544704583</v>
       </c>
       <c r="AD3">
-        <v>101708.3</v>
+        <v>85087</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>101708.3</v>
+        <v>85087</v>
       </c>
       <c r="AG3">
-        <v>96414.10000000001</v>
+        <v>78971.7</v>
       </c>
       <c r="AH3">
-        <v>0.8736250332843731</v>
+        <v>0.8233519317374703</v>
       </c>
       <c r="AI3">
-        <v>0.9138844286621806</v>
+        <v>0.8636134805185315</v>
       </c>
       <c r="AJ3">
-        <v>0.8676043942595306</v>
+        <v>0.8122412624489724</v>
       </c>
       <c r="AK3">
-        <v>0.9095832849834101</v>
+        <v>0.8545879139608545</v>
       </c>
       <c r="AL3">
-        <v>8.470000000000001</v>
+        <v>53.5</v>
       </c>
       <c r="AM3">
-        <v>-141.83</v>
+        <v>-119.4</v>
       </c>
       <c r="AN3">
-        <v>27.77245917754356</v>
+        <v>21.79036058184798</v>
       </c>
       <c r="AO3">
-        <v>352.1369539551357</v>
+        <v>60.26915887850468</v>
       </c>
       <c r="AP3">
-        <v>26.32682540549397</v>
+        <v>20.22426244622003</v>
       </c>
       <c r="AQ3">
-        <v>-21.02940139603751</v>
+        <v>-27.00502512562814</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/italy/italy_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_insurance_life.xlsx
@@ -648,10 +648,10 @@
         <v>0.2343026819113638</v>
       </c>
       <c r="X2">
-        <v>0.3027195557967973</v>
+        <v>0.3026714353888129</v>
       </c>
       <c r="Y2">
-        <v>-0.06841687388543352</v>
+        <v>-0.06836875347744911</v>
       </c>
       <c r="Z2">
         <v>0.1395877311043423</v>
@@ -660,10 +660,10 @@
         <v>0.02149162006831577</v>
       </c>
       <c r="AB2">
-        <v>0.1032640455153616</v>
+        <v>0.1032555451382471</v>
       </c>
       <c r="AC2">
-        <v>-0.08177242544704583</v>
+        <v>-0.08176392506993138</v>
       </c>
       <c r="AD2">
         <v>85087</v>
@@ -785,10 +785,10 @@
         <v>0.2343026819113638</v>
       </c>
       <c r="X3">
-        <v>0.3027195557967973</v>
+        <v>0.3026714353888129</v>
       </c>
       <c r="Y3">
-        <v>-0.06841687388543352</v>
+        <v>-0.06836875347744911</v>
       </c>
       <c r="Z3">
         <v>0.1395877311043423</v>
@@ -797,10 +797,10 @@
         <v>0.02149162006831577</v>
       </c>
       <c r="AB3">
-        <v>0.1032640455153616</v>
+        <v>0.1032555451382471</v>
       </c>
       <c r="AC3">
-        <v>-0.08177242544704583</v>
+        <v>-0.08176392506993138</v>
       </c>
       <c r="AD3">
         <v>85087</v>
